--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008452235047349248</v>
       </c>
       <c r="C2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>39751034</v>
+        <v>4109311</v>
       </c>
       <c r="L2" t="n">
-        <v>21886789</v>
+        <v>1803984</v>
       </c>
       <c r="M2" t="n">
-        <v>5226390</v>
+        <v>331696</v>
       </c>
       <c r="N2" t="n">
-        <v>240108</v>
+        <v>8579</v>
       </c>
       <c r="O2" t="n">
-        <v>3073987</v>
+        <v>188031</v>
       </c>
       <c r="P2" t="n">
-        <v>1200910</v>
+        <v>64992</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999991774559021</v>
+        <v>0.9999763965606689</v>
       </c>
       <c r="R2" t="n">
-        <v>0.860609769821167</v>
+        <v>0.7460672855377197</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7374204993247986</v>
+        <v>0.5719853639602661</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6758739352226257</v>
+        <v>0.4507804811000824</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2785339951515198</v>
+        <v>0.06079869717359543</v>
       </c>
       <c r="V2" t="n">
-        <v>0.726476788520813</v>
+        <v>0.4953842163085938</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8263030648231506</v>
+        <v>0.6624131202697754</v>
       </c>
       <c r="X2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="AG2" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AH2" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AI2" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560797214508057</v>
+        <v>0.9549221992492676</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115321636199951</v>
+        <v>0.912146270275116</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582335114479065</v>
+        <v>0.8583800792694092</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618483662605286</v>
+        <v>0.6608968377113342</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020155668258667</v>
+        <v>0.9020029902458191</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026323576521127</v>
       </c>
       <c r="C3" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>39751034</v>
+        <v>4109311</v>
       </c>
       <c r="E3" t="n">
-        <v>5216353</v>
+        <v>835483</v>
       </c>
       <c r="F3" t="n">
-        <v>129144</v>
+        <v>26585</v>
       </c>
       <c r="G3" t="n">
-        <v>11341</v>
+        <v>2430</v>
       </c>
       <c r="H3" t="n">
-        <v>7188</v>
+        <v>1649</v>
       </c>
       <c r="I3" t="n">
-        <v>483</v>
+        <v>173</v>
       </c>
       <c r="J3" t="n">
-        <v>90149131</v>
+        <v>10016473</v>
       </c>
       <c r="K3" t="n">
-        <v>95412422</v>
+        <v>9955293</v>
       </c>
       <c r="L3" t="n">
-        <v>109682800</v>
+        <v>11673361</v>
       </c>
       <c r="M3" t="n">
-        <v>136049305</v>
+        <v>14985591</v>
       </c>
       <c r="N3" t="n">
-        <v>145540710</v>
+        <v>16107377</v>
       </c>
       <c r="O3" t="n">
-        <v>141220503</v>
+        <v>15626684</v>
       </c>
       <c r="P3" t="n">
-        <v>144973149</v>
+        <v>16102792</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8810923099517822</v>
+        <v>0.8258834481239319</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7421718835830688</v>
+        <v>0.5456162095069885</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6213979721069336</v>
+        <v>0.352913498878479</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2987324595451355</v>
+        <v>0.09564422816038132</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6699298024177551</v>
+        <v>0.3676925897598267</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6898578405380249</v>
+        <v>0.3355534076690674</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="Z3" t="n">
-        <v>1777968</v>
+        <v>196543</v>
       </c>
       <c r="AA3" t="n">
-        <v>76428</v>
+        <v>8427</v>
       </c>
       <c r="AB3" t="n">
-        <v>61298</v>
+        <v>6839</v>
       </c>
       <c r="AC3" t="n">
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90149598</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>99866284</v>
+        <v>11129066</v>
       </c>
       <c r="AG3" t="n">
-        <v>114872156</v>
+        <v>12733718</v>
       </c>
       <c r="AH3" t="n">
-        <v>137364636</v>
+        <v>15256890</v>
       </c>
       <c r="AI3" t="n">
-        <v>145891115</v>
+        <v>16209518</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141928554</v>
+        <v>15768153</v>
       </c>
       <c r="AK3" t="n">
-        <v>145106283</v>
+        <v>16122647</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575262069702148</v>
+        <v>0.95742267370224</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909828245639801</v>
+        <v>0.9092735648155212</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573063611984253</v>
+        <v>0.8566092252731323</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612093448638916</v>
+        <v>0.6602116227149963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014564752578735</v>
+        <v>0.9011421799659729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03197108341586186</v>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>6001373</v>
+        <v>1273751</v>
       </c>
       <c r="E4" t="n">
-        <v>21886789</v>
+        <v>1803984</v>
       </c>
       <c r="F4" t="n">
-        <v>1381389</v>
+        <v>183309</v>
       </c>
       <c r="G4" t="n">
-        <v>78009</v>
+        <v>18180</v>
       </c>
       <c r="H4" t="n">
-        <v>130798</v>
+        <v>24486</v>
       </c>
       <c r="I4" t="n">
-        <v>11779</v>
+        <v>2587</v>
       </c>
       <c r="J4" t="n">
-        <v>467</v>
+        <v>149</v>
       </c>
       <c r="K4" t="n">
-        <v>6438350</v>
+        <v>1398652</v>
       </c>
       <c r="L4" t="n">
-        <v>7793412</v>
+        <v>1349915</v>
       </c>
       <c r="M4" t="n">
-        <v>2506398</v>
+        <v>404130</v>
       </c>
       <c r="N4" t="n">
-        <v>621934</v>
+        <v>132526</v>
       </c>
       <c r="O4" t="n">
-        <v>1157376</v>
+        <v>191535</v>
       </c>
       <c r="P4" t="n">
-        <v>252443</v>
+        <v>33122</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999958872795105</v>
+        <v>0.9999881982803345</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8707305788993835</v>
+        <v>0.783949077129364</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7397885918617249</v>
+        <v>0.5584896802902222</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6474921107292175</v>
+        <v>0.3958882689476013</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2882798612117767</v>
+        <v>0.07434078305959702</v>
       </c>
       <c r="V4" t="n">
-        <v>0.697058379650116</v>
+        <v>0.422092467546463</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7519407868385315</v>
+        <v>0.4454557597637177</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1853220</v>
+        <v>210159</v>
       </c>
       <c r="Z4" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AA4" t="n">
-        <v>745446</v>
+        <v>83023</v>
       </c>
       <c r="AB4" t="n">
-        <v>49654</v>
+        <v>5590</v>
       </c>
       <c r="AC4" t="n">
-        <v>10250</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1984488</v>
+        <v>224879</v>
       </c>
       <c r="AG4" t="n">
-        <v>2604056</v>
+        <v>289558</v>
       </c>
       <c r="AH4" t="n">
-        <v>1191067</v>
+        <v>132831</v>
       </c>
       <c r="AI4" t="n">
-        <v>271529</v>
+        <v>30385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449325</v>
+        <v>50066</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568024277687073</v>
+        <v>0.9561707377433777</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106794595718384</v>
+        <v>0.9107076525688171</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577696084976196</v>
+        <v>0.8574937582015991</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615287065505981</v>
+        <v>0.660554051399231</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017359018325806</v>
+        <v>0.9015724062919617</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>303335</v>
+        <v>92354</v>
       </c>
       <c r="E5" t="n">
-        <v>2117495</v>
+        <v>402141</v>
       </c>
       <c r="F5" t="n">
-        <v>5226390</v>
+        <v>331696</v>
       </c>
       <c r="G5" t="n">
-        <v>202514</v>
+        <v>37251</v>
       </c>
       <c r="H5" t="n">
-        <v>511741</v>
+        <v>67775</v>
       </c>
       <c r="I5" t="n">
-        <v>49187</v>
+        <v>8637</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5364594</v>
+        <v>866344</v>
       </c>
       <c r="L5" t="n">
-        <v>7603399</v>
+        <v>1502340</v>
       </c>
       <c r="M5" t="n">
-        <v>3184307</v>
+        <v>608183</v>
       </c>
       <c r="N5" t="n">
-        <v>563648</v>
+        <v>81118</v>
       </c>
       <c r="O5" t="n">
-        <v>1514534</v>
+        <v>323350</v>
       </c>
       <c r="P5" t="n">
-        <v>539898</v>
+        <v>128694</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999968409538269</v>
+        <v>0.9999908804893494</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9196895360946655</v>
+        <v>0.8612950444221497</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8952358365058899</v>
+        <v>0.8253322243690491</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9612788558006287</v>
+        <v>0.9380074739456177</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9919329881668091</v>
+        <v>0.9869167804718018</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9818195700645447</v>
+        <v>0.9684692025184631</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9946087002754211</v>
+        <v>0.9900906085968018</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72334</v>
+        <v>8098</v>
       </c>
       <c r="Z5" t="n">
-        <v>769884</v>
+        <v>86770</v>
       </c>
       <c r="AA5" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AB5" t="n">
-        <v>89719</v>
+        <v>10018</v>
       </c>
       <c r="AC5" t="n">
-        <v>262519</v>
+        <v>29251</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1916233</v>
+        <v>211850</v>
       </c>
       <c r="AG5" t="n">
-        <v>2659182</v>
+        <v>299971</v>
       </c>
       <c r="AH5" t="n">
-        <v>1200153</v>
+        <v>134770</v>
       </c>
       <c r="AI5" t="n">
-        <v>272305</v>
+        <v>30478</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452169</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734584093093872</v>
+        <v>0.9732553958892822</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641875028610229</v>
+        <v>0.9638981223106384</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837294816970825</v>
+        <v>0.9836125373840332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962996244430542</v>
+        <v>0.99627286195755</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993865966796875</v>
+        <v>0.9938381910324097</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983735084533691</v>
+        <v>0.9983692169189453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>112766</v>
+        <v>21880</v>
       </c>
       <c r="E6" t="n">
-        <v>186100</v>
+        <v>25022</v>
       </c>
       <c r="F6" t="n">
-        <v>182152</v>
+        <v>25422</v>
       </c>
       <c r="G6" t="n">
-        <v>240108</v>
+        <v>8579</v>
       </c>
       <c r="H6" t="n">
-        <v>74969</v>
+        <v>7824</v>
       </c>
       <c r="I6" t="n">
-        <v>7576</v>
+        <v>952</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58491</v>
+        <v>6586</v>
       </c>
       <c r="Z6" t="n">
-        <v>48185</v>
+        <v>5354</v>
       </c>
       <c r="AA6" t="n">
-        <v>98390</v>
+        <v>11038</v>
       </c>
       <c r="AB6" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AC6" t="n">
-        <v>62910</v>
+        <v>7019</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>19981</v>
+        <v>10145</v>
       </c>
       <c r="E7" t="n">
-        <v>252264</v>
+        <v>79127</v>
       </c>
       <c r="F7" t="n">
-        <v>760570</v>
+        <v>150542</v>
       </c>
       <c r="G7" t="n">
-        <v>298272</v>
+        <v>62750</v>
       </c>
       <c r="H7" t="n">
-        <v>3073987</v>
+        <v>188031</v>
       </c>
       <c r="I7" t="n">
-        <v>183418</v>
+        <v>20773</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7290</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267822</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68465</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="D8" t="n">
-        <v>895</v>
+        <v>522</v>
       </c>
       <c r="E8" t="n">
-        <v>21200</v>
+        <v>8142</v>
       </c>
       <c r="F8" t="n">
-        <v>53143</v>
+        <v>18272</v>
       </c>
       <c r="G8" t="n">
-        <v>31798</v>
+        <v>11915</v>
       </c>
       <c r="H8" t="n">
-        <v>432680</v>
+        <v>89801</v>
       </c>
       <c r="I8" t="n">
-        <v>1200910</v>
+        <v>64992</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
